--- a/artfynd/A 50728-2022 artfynd.xlsx
+++ b/artfynd/A 50728-2022 artfynd.xlsx
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117711765</v>
+        <v>117711587</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>79562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,21 +1627,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465105</v>
+        <v>465115</v>
       </c>
       <c r="R11" t="n">
-        <v>6822680</v>
+        <v>6822796</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117711587</v>
+        <v>117711765</v>
       </c>
       <c r="B12" t="n">
-        <v>79562</v>
+        <v>78480</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,21 +1729,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465115</v>
+        <v>465105</v>
       </c>
       <c r="R12" t="n">
-        <v>6822796</v>
+        <v>6822680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 50728-2022 artfynd.xlsx
+++ b/artfynd/A 50728-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117711772</v>
+        <v>117711559</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>79590</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465258</v>
+        <v>465044</v>
       </c>
       <c r="R2" t="n">
-        <v>6822696</v>
+        <v>6822619</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +756,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117711675</v>
+        <v>117711566</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>79590</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +798,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465115</v>
+        <v>465130</v>
       </c>
       <c r="R3" t="n">
-        <v>6822797</v>
+        <v>6822768</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +867,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117711734</v>
+        <v>117711735</v>
       </c>
       <c r="B4" t="n">
-        <v>90517</v>
+        <v>78480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465126</v>
+        <v>465135</v>
       </c>
       <c r="R4" t="n">
-        <v>6822834</v>
+        <v>6822833</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,7 +980,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mitt i planerad körväg</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117711821</v>
+        <v>117711587</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>79562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465185</v>
+        <v>465115</v>
       </c>
       <c r="R5" t="n">
-        <v>6822757</v>
+        <v>6822796</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117711913</v>
+        <v>117711675</v>
       </c>
       <c r="B6" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465106</v>
+        <v>465115</v>
       </c>
       <c r="R6" t="n">
-        <v>6822818</v>
+        <v>6822797</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117711764</v>
+        <v>117711734</v>
       </c>
       <c r="B7" t="n">
-        <v>78480</v>
+        <v>90517</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,34 +1228,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465109</v>
+        <v>465126</v>
       </c>
       <c r="R7" t="n">
-        <v>6822696</v>
+        <v>6822834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,12 +1293,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mitt i planerad körväg</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1296,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117711559</v>
+        <v>117711764</v>
       </c>
       <c r="B8" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,41 +1335,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465044</v>
+        <v>465109</v>
       </c>
       <c r="R8" t="n">
-        <v>6822619</v>
+        <v>6822696</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,18 +1401,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1407,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117711914</v>
+        <v>117711765</v>
       </c>
       <c r="B9" t="n">
         <v>78480</v>
@@ -1447,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465107</v>
+        <v>465105</v>
       </c>
       <c r="R9" t="n">
-        <v>6822816</v>
+        <v>6822680</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117711850</v>
+        <v>117711914</v>
       </c>
       <c r="B10" t="n">
         <v>78480</v>
@@ -1549,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465139</v>
+        <v>465107</v>
       </c>
       <c r="R10" t="n">
-        <v>6822842</v>
+        <v>6822816</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117711587</v>
+        <v>117711850</v>
       </c>
       <c r="B11" t="n">
-        <v>79562</v>
+        <v>78480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465115</v>
+        <v>465139</v>
       </c>
       <c r="R11" t="n">
-        <v>6822796</v>
+        <v>6822842</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117711765</v>
+        <v>117711565</v>
       </c>
       <c r="B12" t="n">
-        <v>78480</v>
+        <v>79590</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,38 +1743,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465105</v>
+        <v>465115</v>
       </c>
       <c r="R12" t="n">
-        <v>6822680</v>
+        <v>6822797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,12 +1812,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1815,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117711565</v>
+        <v>117711772</v>
       </c>
       <c r="B13" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,41 +1854,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465115</v>
+        <v>465258</v>
       </c>
       <c r="R13" t="n">
-        <v>6822797</v>
+        <v>6822696</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,18 +1920,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1926,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117711566</v>
+        <v>117711821</v>
       </c>
       <c r="B14" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1938,41 +1956,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465130</v>
+        <v>465185</v>
       </c>
       <c r="R14" t="n">
-        <v>6822768</v>
+        <v>6822757</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,18 +2022,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2037,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117711735</v>
+        <v>117711848</v>
       </c>
       <c r="B15" t="n">
         <v>78480</v>
@@ -2071,19 +2080,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465135</v>
+        <v>465126</v>
       </c>
       <c r="R15" t="n">
-        <v>6822833</v>
+        <v>6822829</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,18 +2124,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117711848</v>
+        <v>117711913</v>
       </c>
       <c r="B16" t="n">
         <v>78480</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465126</v>
+        <v>465106</v>
       </c>
       <c r="R16" t="n">
-        <v>6822829</v>
+        <v>6822818</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 50728-2022 artfynd.xlsx
+++ b/artfynd/A 50728-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117711559</v>
+        <v>117711821</v>
       </c>
       <c r="B2" t="n">
-        <v>79590</v>
+        <v>78482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465044</v>
+        <v>465185</v>
       </c>
       <c r="R2" t="n">
-        <v>6822619</v>
+        <v>6822757</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,18 +753,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117711566</v>
+        <v>117711734</v>
       </c>
       <c r="B3" t="n">
-        <v>79590</v>
+        <v>90519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465130</v>
+        <v>465126</v>
       </c>
       <c r="R3" t="n">
-        <v>6822768</v>
+        <v>6822834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +860,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Mitt i planerad körväg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117711735</v>
+        <v>117711675</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>79563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,37 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465135</v>
+        <v>465115</v>
       </c>
       <c r="R4" t="n">
-        <v>6822833</v>
+        <v>6822797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,18 +966,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1008,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117711587</v>
+        <v>117711914</v>
       </c>
       <c r="B5" t="n">
-        <v>79562</v>
+        <v>78482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465115</v>
+        <v>465107</v>
       </c>
       <c r="R5" t="n">
-        <v>6822796</v>
+        <v>6822816</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117711675</v>
+        <v>117711587</v>
       </c>
       <c r="B6" t="n">
-        <v>79561</v>
+        <v>79564</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,7 +1135,7 @@
         <v>465115</v>
       </c>
       <c r="R6" t="n">
-        <v>6822797</v>
+        <v>6822796</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117711734</v>
+        <v>117711559</v>
       </c>
       <c r="B7" t="n">
-        <v>90517</v>
+        <v>79592</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465126</v>
+        <v>465044</v>
       </c>
       <c r="R7" t="n">
-        <v>6822834</v>
+        <v>6822619</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1277,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Mitt i planerad körväg</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117711764</v>
+        <v>117711850</v>
       </c>
       <c r="B8" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465109</v>
+        <v>465139</v>
       </c>
       <c r="R8" t="n">
-        <v>6822696</v>
+        <v>6822842</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117711765</v>
+        <v>117711764</v>
       </c>
       <c r="B9" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465105</v>
+        <v>465109</v>
       </c>
       <c r="R9" t="n">
-        <v>6822680</v>
+        <v>6822696</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117711914</v>
+        <v>117711848</v>
       </c>
       <c r="B10" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465107</v>
+        <v>465126</v>
       </c>
       <c r="R10" t="n">
-        <v>6822816</v>
+        <v>6822829</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117711850</v>
+        <v>117711735</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,16 +1645,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465139</v>
+        <v>465135</v>
       </c>
       <c r="R11" t="n">
-        <v>6822842</v>
+        <v>6822833</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,12 +1692,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1731,10 +1722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117711565</v>
+        <v>117711913</v>
       </c>
       <c r="B12" t="n">
-        <v>79590</v>
+        <v>78482</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,41 +1734,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465115</v>
+        <v>465106</v>
       </c>
       <c r="R12" t="n">
-        <v>6822797</v>
+        <v>6822818</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,18 +1800,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1845,7 +1827,7 @@
         <v>117711772</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,10 +1926,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117711821</v>
+        <v>117711765</v>
       </c>
       <c r="B14" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,10 +1966,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465185</v>
+        <v>465105</v>
       </c>
       <c r="R14" t="n">
-        <v>6822757</v>
+        <v>6822680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,10 +2028,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117711848</v>
+        <v>117711565</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>79592</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2058,38 +2040,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465126</v>
+        <v>465115</v>
       </c>
       <c r="R15" t="n">
-        <v>6822829</v>
+        <v>6822797</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,12 +2109,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2148,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117711913</v>
+        <v>117711566</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>79592</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,38 +2151,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465106</v>
+        <v>465130</v>
       </c>
       <c r="R16" t="n">
-        <v>6822818</v>
+        <v>6822768</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2226,12 +2220,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50728-2022 artfynd.xlsx
+++ b/artfynd/A 50728-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117711914</v>
+        <v>117711402</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465107</v>
+        <v>465170</v>
       </c>
       <c r="R2" t="n">
-        <v>6822816</v>
+        <v>6822729</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117711675</v>
+        <v>117711409</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465115</v>
+        <v>465107</v>
       </c>
       <c r="R3" t="n">
-        <v>6822797</v>
+        <v>6822783</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117711850</v>
+        <v>117711410</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465139</v>
+        <v>465104</v>
       </c>
       <c r="R4" t="n">
-        <v>6822842</v>
+        <v>6822785</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117711848</v>
+        <v>117711730</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465126</v>
+        <v>465146</v>
       </c>
       <c r="R5" t="n">
-        <v>6822829</v>
+        <v>6822800</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117711913</v>
+        <v>117711587</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465106</v>
+        <v>465115</v>
       </c>
       <c r="R6" t="n">
-        <v>6822818</v>
+        <v>6822796</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117711764</v>
+        <v>119549076</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1171,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465109</v>
+        <v>465493</v>
       </c>
       <c r="R7" t="n">
-        <v>6822696</v>
+        <v>6822703</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1234,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,15 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117711734</v>
+        <v>119549077</v>
       </c>
       <c r="B8" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,37 +1277,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465126</v>
+        <v>465527</v>
       </c>
       <c r="R8" t="n">
-        <v>6822834</v>
+        <v>6822634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,17 +1340,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mitt i planerad körväg</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1354,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1398,37 +1372,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117711565</v>
+        <v>117711735</v>
       </c>
       <c r="B9" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1441,10 +1410,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465115</v>
+        <v>465135</v>
       </c>
       <c r="R9" t="n">
-        <v>6822797</v>
+        <v>6822833</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,7 +1450,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,53 +1478,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117711559</v>
+        <v>117711759</v>
       </c>
       <c r="B10" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465044</v>
+        <v>465025</v>
       </c>
       <c r="R10" t="n">
-        <v>6822619</v>
+        <v>6822630</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,18 +1551,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1620,19 +1575,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117711772</v>
+        <v>117711761</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1660,10 +1610,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465258</v>
+        <v>465039</v>
       </c>
       <c r="R11" t="n">
-        <v>6822696</v>
+        <v>6822657</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,37 +1672,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117711587</v>
+        <v>117711762</v>
       </c>
       <c r="B12" t="n">
-        <v>79566</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1762,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465115</v>
+        <v>465053</v>
       </c>
       <c r="R12" t="n">
-        <v>6822796</v>
+        <v>6822667</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,53 +1769,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117711566</v>
+        <v>117711763</v>
       </c>
       <c r="B13" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465130</v>
+        <v>465048</v>
       </c>
       <c r="R13" t="n">
-        <v>6822768</v>
+        <v>6822660</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,18 +1842,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1935,19 +1866,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117711765</v>
+        <v>117711764</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1975,10 +1901,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465105</v>
+        <v>465109</v>
       </c>
       <c r="R14" t="n">
-        <v>6822680</v>
+        <v>6822696</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,19 +1963,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117711735</v>
+        <v>117711765</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2071,19 +1992,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465135</v>
+        <v>465105</v>
       </c>
       <c r="R15" t="n">
-        <v>6822833</v>
+        <v>6822680</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,18 +2036,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2148,19 +2060,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117711821</v>
+        <v>117711766</v>
       </c>
       <c r="B16" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2188,10 +2095,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465185</v>
+        <v>465122</v>
       </c>
       <c r="R16" t="n">
-        <v>6822757</v>
+        <v>6822673</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2247,6 +2154,3965 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>117711772</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>465258</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6822696</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>117711773</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>465256</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6822710</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>117711819</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>465191</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6822805</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>117711820</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>465186</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6822793</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>117711821</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>465185</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6822757</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>117711822</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>465170</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6822724</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>117711823</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>465157</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6822719</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>117711841</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>465060</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6822671</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>117711842</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>465106</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6822702</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>117711843</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>465110</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6822717</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>117711845</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>465139</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6822785</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>117711846</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>465149</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6822795</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>117711847</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>465136</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6822815</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>117711848</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>465126</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6822829</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>117711850</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>465139</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6822842</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>117711851</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>465136</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6822847</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>117711852</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>465132</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6822856</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>117711853</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>465129</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6822859</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>117711912</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>465072</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6822834</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>117711913</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>465106</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6822818</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>117711914</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>465107</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6822816</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>117711915</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>465102</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6822788</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>117711916</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>465096</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6822795</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>117711917</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>465092</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6822793</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>117711918</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>465083</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6822781</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>117711698</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>465299</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6822674</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>117711468</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>465151</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6822788</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>117711493</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>465091</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6822828</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>117711674</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>465071</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6822839</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>117711675</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>465115</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6822796</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>117711677</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>465112</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6822781</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt, på sälg</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>117711559</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>465044</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6822619</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>117711563</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>465121</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6822755</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>117711565</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>465115</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6822796</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>117711566</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>465130</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6822768</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>117712007</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>465087</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6822688</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>117711581</v>
+      </c>
+      <c r="B53" t="n">
+        <v>83305</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>465153</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6822716</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>117711537</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>465167</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6822725</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>117711543</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>465107</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6822869</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>117711378</v>
+      </c>
+      <c r="B56" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>465023</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6822630</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50728-2022 artfynd.xlsx
+++ b/artfynd/A 50728-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711402</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711409</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711410</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711730</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711587</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549076</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549077</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711735</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1572,6 +1617,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711759</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711761</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1766,6 +1821,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711762</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1863,6 +1923,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711763</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1960,6 +2025,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711764</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2057,6 +2127,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711765</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2154,6 +2229,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711766</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2251,6 +2331,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711772</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2348,6 +2433,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711773</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2445,6 +2535,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711819</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2542,6 +2637,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711820</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2639,6 +2739,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711821</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2736,6 +2841,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711822</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2833,6 +2943,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711823</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2930,6 +3045,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711841</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3027,6 +3147,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711842</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3124,6 +3249,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711843</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3221,6 +3351,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711845</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3318,6 +3453,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711846</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3415,6 +3555,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711847</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3512,6 +3657,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711848</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3609,6 +3759,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711850</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3706,6 +3861,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711851</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3803,6 +3963,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711852</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3900,6 +4065,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711853</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3997,6 +4167,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711912</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4094,6 +4269,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711913</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4191,6 +4371,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711914</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4288,6 +4473,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711915</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4385,6 +4575,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711916</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4482,6 +4677,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711917</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4579,6 +4779,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711918</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4676,6 +4881,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711698</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4773,6 +4983,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711468</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4870,6 +5085,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711493</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4967,6 +5187,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711674</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5064,6 +5289,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711675</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5170,6 +5400,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711677</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5276,6 +5511,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711559</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5382,6 +5622,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711563</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5488,6 +5733,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711565</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5594,6 +5844,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711566</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5691,6 +5946,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117712007</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5792,6 +6052,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711581</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5897,6 +6162,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711537</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6006,6 +6276,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711543</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6113,8 +6388,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711378</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>